--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_303_R31.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_303_R31.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4077</v>
+        <v>5.8225</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0376</v>
+        <v>4.0162</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3702</v>
+        <v>1.8062</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8636</v>
+        <v>5.6722</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5654</v>
+        <v>2.6844</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2982</v>
+        <v>2.9879</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0386</v>
+        <v>4.6214</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8437</v>
+        <v>1.6805</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1949</v>
+        <v>2.9409</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.175</v>
+        <v>1.0508</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7217</v>
+        <v>1.0039</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8966</v>
+        <v>0.047</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S2" t="n">
-        <v>2.222</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9268</v>
+        <v>-0.6051</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2952</v>
+        <v>0.5234</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0497</v>
+        <v>5.143</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2771</v>
+        <v>5.2433</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7726</v>
+        <v>-0.1003</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6722</v>
+        <v>2.8636</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6844</v>
+        <v>1.5654</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9879</v>
+        <v>1.2982</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6214</v>
+        <v>3.0386</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6805</v>
+        <v>0.8437</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9409</v>
+        <v>2.1949</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0508</v>
+        <v>-0.175</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0039</v>
+        <v>0.7217</v>
       </c>
       <c r="O3" t="n">
-        <v>0.047</v>
+        <v>-0.8966</v>
       </c>
       <c r="P3" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8544</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3443</v>
+        <v>1.1325</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4898</v>
+        <v>-0.1753</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0301</v>
+        <v>3.3924</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2014</v>
+        <v>2.5666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8287</v>
+        <v>0.8257</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2318</v>
+        <v>2.9649</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6998</v>
+        <v>-0.1836</v>
       </c>
       <c r="I4" t="n">
-        <v>0.532</v>
+        <v>3.1485</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8287</v>
+        <v>2.3503</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3466</v>
+        <v>-0.4334</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4821</v>
+        <v>2.7837</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5969</v>
+        <v>0.6146</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3532</v>
+        <v>0.2499</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9500999999999999</v>
+        <v>0.3648</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7108</v>
+        <v>-0.2684</v>
       </c>
       <c r="T4" t="n">
-        <v>0.767</v>
+        <v>0.2164</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0562</v>
+        <v>-0.4848</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8483</v>
+        <v>2.9346</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1546</v>
+        <v>2.3075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6937</v>
+        <v>0.6271</v>
       </c>
       <c r="G5" t="n">
-        <v>2.153</v>
+        <v>1.2318</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5473</v>
+        <v>0.6998</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6057</v>
+        <v>0.532</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4595</v>
+        <v>1.8287</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0609</v>
+        <v>0.3466</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3986</v>
+        <v>1.4821</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6936</v>
+        <v>-0.5969</v>
       </c>
       <c r="N5" t="n">
-        <v>1.4864</v>
+        <v>0.3532</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7929</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4659</v>
+        <v>0.6152</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0895</v>
+        <v>0.8731</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3765</v>
+        <v>-0.2579</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4665</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
         <v>-0.3943</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6271</v>
+        <v>1.7787</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9022</v>
+        <v>1.1613</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7249</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9649</v>
+        <v>1.7394</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1836</v>
+        <v>0.5416</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1485</v>
+        <v>1.1979</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3503</v>
+        <v>1.7036</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4334</v>
+        <v>0.1344</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7837</v>
+        <v>1.5692</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6146</v>
+        <v>0.0358</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2499</v>
+        <v>0.4071</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3648</v>
+        <v>-0.3713</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0337</v>
+        <v>-0.1926</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4481</v>
+        <v>-0.5423</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5856</v>
+        <v>0.3497</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0813</v>
+        <v>1.4258</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7328</v>
+        <v>1.9509</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3486</v>
+        <v>-0.5251</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7394</v>
+        <v>-0.4377</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5416</v>
+        <v>0.3253</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1979</v>
+        <v>-0.763</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7036</v>
+        <v>0.7668</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1344</v>
+        <v>0.1078</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5692</v>
+        <v>0.659</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0358</v>
+        <v>-1.2044</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4071</v>
+        <v>0.2175</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3713</v>
+        <v>-1.422</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.89</v>
+        <v>0.2399</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9709</v>
+        <v>0.9006</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0808</v>
+        <v>-0.6607</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8318</v>
+        <v>1.1886</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7499</v>
+        <v>0.9318</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0819</v>
+        <v>0.2568</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7573</v>
+        <v>2.153</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5967</v>
+        <v>1.5473</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1605</v>
+        <v>0.6057</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0576</v>
+        <v>1.4595</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6785</v>
+        <v>0.0609</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7361</v>
+        <v>1.3986</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8148</v>
+        <v>0.6936</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0818</v>
+        <v>1.4864</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8966</v>
+        <v>-0.7929</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7308</v>
+        <v>-0.1937</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8521</v>
+        <v>-0.1333</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1212</v>
+        <v>-0.0604</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1418</v>
+        <v>-1.4665</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6703</v>
+        <v>0.4035</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3297</v>
+        <v>0.4064</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6595</v>
+        <v>-0.0029</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4377</v>
+        <v>0.2521</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3253</v>
+        <v>-0.3301</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.763</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7668</v>
+        <v>0.1272</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1078</v>
+        <v>0.0168</v>
       </c>
       <c r="L9" t="n">
-        <v>0.659</v>
+        <v>0.1104</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2044</v>
+        <v>0.1249</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2175</v>
+        <v>-0.3469</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.422</v>
+        <v>0.4718</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5157</v>
+        <v>0.1513</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2794</v>
+        <v>0.2792</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7951</v>
+        <v>-0.1278</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3357</v>
+        <v>0.3139</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1739</v>
+        <v>0.0303</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5096</v>
+        <v>0.2835</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0184</v>
+        <v>-0.7573</v>
       </c>
       <c r="H10" t="n">
-        <v>3.036</v>
+        <v>-0.5967</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0176</v>
+        <v>-0.1605</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1032</v>
+        <v>0.0576</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1678</v>
+        <v>-0.6785</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0646</v>
+        <v>0.7361</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9151</v>
+        <v>-0.8148</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8681</v>
+        <v>0.0818</v>
       </c>
       <c r="O10" t="n">
-        <v>0.047</v>
+        <v>-0.8966</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2451</v>
+        <v>1.2129</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2592</v>
+        <v>1.1325</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5043</v>
+        <v>0.0804</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.1418</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0176</v>
+        <v>0.1415</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0525</v>
+        <v>-1.0992</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0701</v>
+        <v>1.2408</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2521</v>
+        <v>1.0184</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3301</v>
+        <v>3.036</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5822000000000001</v>
+        <v>-2.0176</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1272</v>
+        <v>0.1032</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0168</v>
+        <v>2.1678</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1104</v>
+        <v>-2.0646</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1249</v>
+        <v>0.9151</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3469</v>
+        <v>0.8681</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4718</v>
+        <v>0.047</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2697</v>
+        <v>0.051</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0747</v>
+        <v>-0.1845</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.195</v>
+        <v>0.2355</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.821</v>
+        <v>-1.2677</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6331</v>
+        <v>-1.2478</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1879</v>
+        <v>-0.0199</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3302</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4187</v>
+        <v>0.1346</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3541</v>
+        <v>0.7393</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.6047</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.54</v>
+        <v>-1.2797</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9588</v>
+        <v>-2.1017</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4187</v>
+        <v>0.822</v>
       </c>
       <c r="G13" t="n">
         <v>0.4431</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6456</v>
+        <v>-0.3853</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4189</v>
+        <v>-0.5619</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2267</v>
+        <v>0.1766</v>
       </c>
       <c r="V13" t="n">
         <v>1.214</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.5034</v>
+        <v>19.9971</v>
       </c>
       <c r="E14" t="n">
-        <v>12.672</v>
+        <v>14.1656</v>
       </c>
       <c r="F14" t="n">
-        <v>5.831399999999999</v>
+        <v>5.8313</v>
       </c>
       <c r="G14" t="n">
         <v>14.8133</v>
       </c>
       <c r="H14" t="n">
-        <v>6.398600000000001</v>
+        <v>6.398599999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>8.415000000000001</v>
+        <v>8.414999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>14.7952</v>
@@ -1528,10 +1528,10 @@
         <v>14.5035</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01830000000000037</v>
+        <v>0.01830000000000015</v>
       </c>
       <c r="N14" t="n">
-        <v>6.1068</v>
+        <v>6.106800000000002</v>
       </c>
       <c r="O14" t="n">
         <v>-6.088400000000001</v>
@@ -1546,16 +1546,16 @@
         <v>9.2784</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7467999999999995</v>
+        <v>2.2404</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7528</v>
+        <v>3.246500000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0059</v>
+        <v>-1.006</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5361000000000002</v>
+        <v>-0.5360999999999998</v>
       </c>
       <c r="W14" t="n">
         <v>1.923</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8707</v>
+        <v>3.5277</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3798</v>
+        <v>4.9696</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5091</v>
+        <v>-1.4419</v>
       </c>
       <c r="G15" t="n">
         <v>2.4729</v>
@@ -1624,13 +1624,13 @@
         <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2801</v>
+        <v>-0.6231</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2617</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0184</v>
+        <v>0.0488</v>
       </c>
       <c r="V15" t="n">
         <v>1.214</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4245</v>
+        <v>1.2609</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3402</v>
+        <v>1.6941</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9157</v>
+        <v>-0.4332</v>
       </c>
       <c r="G16" t="n">
         <v>0.6367</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5679999999999999</v>
+        <v>0.2684</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2715</v>
+        <v>0.6253</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8395</v>
+        <v>-0.3569</v>
       </c>
       <c r="V16" t="n">
         <v>0.8197</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3707</v>
+        <v>0.2877</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.159</v>
+        <v>-0.5959</v>
       </c>
       <c r="G17" t="n">
         <v>-0.074</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>1.053</v>
+        <v>0.97</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2715</v>
+        <v>0.6253</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7815</v>
+        <v>0.3446</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6025</v>
+        <v>-0.4902</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0306</v>
+        <v>0.7947</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6331</v>
+        <v>-1.2849</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4707</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3431</v>
+        <v>-0.2309</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3181</v>
+        <v>-0.554</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.025</v>
+        <v>0.3231</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2525</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.486</v>
+        <v>-1.5173</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4295</v>
+        <v>-1.2723</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0564</v>
+        <v>-0.245</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9283</v>
+        <v>-3.7695</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4766</v>
+        <v>-2.3074</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4517</v>
+        <v>-1.4621</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9997</v>
+        <v>-1.9647</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.287</v>
+        <v>-1.717</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7127</v>
+        <v>-0.2477</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07140000000000001</v>
+        <v>-1.8048</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1896</v>
+        <v>-0.5904</v>
       </c>
       <c r="O19" t="n">
-        <v>0.261</v>
+        <v>-1.2144</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4424</v>
+        <v>0.5357</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5702</v>
+        <v>0.6923</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1278</v>
+        <v>-0.1566</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5738</v>
+        <v>-1.7897</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2723</v>
+        <v>-1.9013</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3015</v>
+        <v>0.1116</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.7695</v>
+        <v>-1.9283</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3074</v>
+        <v>-1.4766</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4621</v>
+        <v>-0.4517</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9647</v>
+        <v>-1.9997</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.717</v>
+        <v>-1.287</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2477</v>
+        <v>-0.7127</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8048</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5904</v>
+        <v>-0.1896</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2144</v>
+        <v>0.261</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4793</v>
+        <v>0.1386</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6923</v>
+        <v>0.0984</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2131</v>
+        <v>0.0402</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1372</v>
+        <v>-2.2915</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3127</v>
+        <v>-1.5592</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8245</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.3566</v>
+        <v>-1.2311</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7334000000000001</v>
+        <v>1.1212</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6232</v>
+        <v>-2.3523</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.131</v>
+        <v>0.0484</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6687</v>
+        <v>1.0825</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4623</v>
+        <v>-1.0341</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2256</v>
+        <v>-1.2795</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.0387</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1609</v>
+        <v>-1.3182</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6137</v>
+        <v>-0.1327</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6765</v>
+        <v>-0.4479</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.06279999999999999</v>
+        <v>0.3152</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3974</v>
+        <v>-2.3062</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2053</v>
+        <v>-1.6485</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1921</v>
+        <v>-0.6577</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2311</v>
+        <v>-1.3504</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1212</v>
+        <v>-0.514</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3523</v>
+        <v>-0.8365</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0484</v>
+        <v>-0.1643</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0825</v>
+        <v>-0.9103</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.0341</v>
+        <v>0.746</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2795</v>
+        <v>-1.1861</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0387</v>
+        <v>0.3963</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3182</v>
+        <v>-1.5825</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2385</v>
+        <v>0.1318</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.094</v>
+        <v>0.2992</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1445</v>
+        <v>-0.1674</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6981</v>
+        <v>-2.569</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4126</v>
+        <v>-1.6665</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2854</v>
+        <v>-0.9025</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3504</v>
+        <v>-3.3566</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.514</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8365</v>
+        <v>-2.6232</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1643</v>
+        <v>-2.131</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9103</v>
+        <v>-0.6687</v>
       </c>
       <c r="L23" t="n">
-        <v>0.746</v>
+        <v>-1.4623</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1861</v>
+        <v>-1.2256</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3963</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5825</v>
+        <v>-1.1609</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2601</v>
+        <v>0.1819</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5351</v>
+        <v>0.3227</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7951</v>
+        <v>-0.1408</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7424</v>
+        <v>-3.3069</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1066</v>
+        <v>-1.9618</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6358</v>
+        <v>-1.3451</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7829</v>
+        <v>-3.3719</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7395</v>
+        <v>-0.7286</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0435</v>
+        <v>-2.6433</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6287</v>
+        <v>-2.2214</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2715</v>
+        <v>-0.6855</v>
       </c>
       <c r="L24" t="n">
-        <v>1.6428</v>
+        <v>-1.5359</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1542</v>
+        <v>-1.1505</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5321</v>
+        <v>-0.0431</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6862</v>
+        <v>-1.1074</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2725</v>
+        <v>-0.5612</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8417</v>
+        <v>0.2596</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4308</v>
+        <v>-0.8208</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.6083</v>
+        <v>0.3943</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6083</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1826</v>
+        <v>-3.4178</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6695</v>
+        <v>-1.0896</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5131</v>
+        <v>-2.3282</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.3719</v>
+        <v>-0.5875</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7286</v>
+        <v>-0.4369</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.6433</v>
+        <v>-0.1506</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.2214</v>
+        <v>1.4891</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6855</v>
+        <v>0.007</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5359</v>
+        <v>1.4821</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1505</v>
+        <v>-2.0766</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0431</v>
+        <v>-0.4439</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1074</v>
+        <v>-1.6327</v>
       </c>
       <c r="P25" t="n">
-        <v>0.232</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R25" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4369</v>
+        <v>-0.5493</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4481</v>
+        <v>-0.2592</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9889</v>
+        <v>-0.2902</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3943</v>
+        <v>-0.4254</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3943</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3494</v>
+        <v>-4.3182</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5614</v>
+        <v>-2.9322</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.788</v>
+        <v>-1.3859</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5875</v>
+        <v>-1.7829</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4369</v>
+        <v>-1.7395</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1506</v>
+        <v>-0.0435</v>
       </c>
       <c r="J26" t="n">
-        <v>1.4891</v>
+        <v>-0.6287</v>
       </c>
       <c r="K26" t="n">
-        <v>0.007</v>
+        <v>-2.2715</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4821</v>
+        <v>1.6428</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.0766</v>
+        <v>-1.1542</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4439</v>
+        <v>0.5321</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.6327</v>
+        <v>-1.6862</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.8556</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q26" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.4809</v>
+        <v>0.6967</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.731</v>
+        <v>0.016</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7499</v>
+        <v>0.6807</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.4254</v>
+        <v>-1.6083</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.4254</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.5035</v>
+        <v>-16.9305</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.689599999999999</v>
+        <v>-5.689400000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-12.8137</v>
+        <v>-11.2411</v>
       </c>
       <c r="G27" t="n">
         <v>-14.8133</v>
@@ -2530,13 +2530,13 @@
         <v>-6.3986</v>
       </c>
       <c r="I27" t="n">
-        <v>-8.414899999999999</v>
+        <v>-8.414900000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.01839999999999908</v>
+        <v>-0.01839999999999953</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.106800000000001</v>
+        <v>-6.1068</v>
       </c>
       <c r="L27" t="n">
         <v>6.088500000000001</v>
@@ -2560,16 +2560,16 @@
         <v>5.798999999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.7467000000000001</v>
+        <v>0.8258999999999997</v>
       </c>
       <c r="T27" t="n">
-        <v>1.0059</v>
+        <v>1.0058</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.7527</v>
+        <v>-0.1801</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5361000000000004</v>
+        <v>0.5361</v>
       </c>
       <c r="W27" t="n">
         <v>2.6009</v>
